--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVIII/LTAIPT_A63F28A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVIII/LTAIPT_A63F28A.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="7365"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -17,40 +17,30 @@
     <sheet name="Hidden_7" sheetId="8" r:id="rId8"/>
     <sheet name="Hidden_8" sheetId="9" r:id="rId9"/>
     <sheet name="Hidden_9" sheetId="10" r:id="rId10"/>
-    <sheet name="Hidden_10" sheetId="11" r:id="rId11"/>
-    <sheet name="Tabla_436444" sheetId="12" r:id="rId12"/>
-    <sheet name="Hidden_1_Tabla_436444" sheetId="13" r:id="rId13"/>
-    <sheet name="Tabla_436473" sheetId="14" r:id="rId14"/>
-    <sheet name="Hidden_1_Tabla_436473" sheetId="15" r:id="rId15"/>
-    <sheet name="Tabla_436474" sheetId="16" r:id="rId16"/>
-    <sheet name="Hidden_1_Tabla_436474" sheetId="17" r:id="rId17"/>
-    <sheet name="Tabla_436475" sheetId="18" r:id="rId18"/>
-    <sheet name="Hidden_1_Tabla_436475" sheetId="19" r:id="rId19"/>
-    <sheet name="Tabla_436476" sheetId="20" r:id="rId20"/>
-    <sheet name="Tabla_436477" sheetId="21" r:id="rId21"/>
+    <sheet name="Tabla_436444" sheetId="11" r:id="rId11"/>
+    <sheet name="Tabla_436473" sheetId="12" r:id="rId12"/>
+    <sheet name="Tabla_436474" sheetId="13" r:id="rId13"/>
+    <sheet name="Tabla_436475" sheetId="14" r:id="rId14"/>
+    <sheet name="Tabla_436476" sheetId="15" r:id="rId15"/>
+    <sheet name="Tabla_436477" sheetId="16" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_1_Tabla_4364446">Hidden_1_Tabla_436444!$A$1:$A$2</definedName>
-    <definedName name="Hidden_1_Tabla_4364736">Hidden_1_Tabla_436473!$A$1:$A$2</definedName>
-    <definedName name="Hidden_1_Tabla_4364746">Hidden_1_Tabla_436474!$A$1:$A$2</definedName>
-    <definedName name="Hidden_1_Tabla_4364755">Hidden_1_Tabla_436475!$A$1:$A$2</definedName>
-    <definedName name="Hidden_1071">Hidden_10!$A$1:$A$2</definedName>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$3</definedName>
     <definedName name="Hidden_25">Hidden_2!$A$1:$A$5</definedName>
     <definedName name="Hidden_36">Hidden_3!$A$1:$A$2</definedName>
-    <definedName name="Hidden_423">Hidden_4!$A$1:$A$2</definedName>
-    <definedName name="Hidden_525">Hidden_5!$A$1:$A$26</definedName>
-    <definedName name="Hidden_629">Hidden_6!$A$1:$A$41</definedName>
-    <definedName name="Hidden_736">Hidden_7!$A$1:$A$32</definedName>
-    <definedName name="Hidden_863">Hidden_8!$A$1:$A$3</definedName>
-    <definedName name="Hidden_970">Hidden_9!$A$1:$A$3</definedName>
+    <definedName name="Hidden_424">Hidden_4!$A$1:$A$26</definedName>
+    <definedName name="Hidden_528">Hidden_5!$A$1:$A$41</definedName>
+    <definedName name="Hidden_635">Hidden_6!$A$1:$A$32</definedName>
+    <definedName name="Hidden_762">Hidden_7!$A$1:$A$3</definedName>
+    <definedName name="Hidden_869">Hidden_8!$A$1:$A$3</definedName>
+    <definedName name="Hidden_970">Hidden_9!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="397">
   <si>
     <t>48983</t>
   </si>
@@ -161,9 +151,6 @@
   </si>
   <si>
     <t>436484</t>
-  </si>
-  <si>
-    <t>571936</t>
   </si>
   <si>
     <t>436491</t>
@@ -413,9 +400,6 @@
     <t>Razón social del contratista o proveedor</t>
   </si>
   <si>
-    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFC de la persona física o moral contratista o proveedor </t>
   </si>
   <si>
@@ -592,63 +576,78 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2021</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>6227604</t>
+    <t>865638</t>
   </si>
   <si>
     <t>ver nota</t>
   </si>
   <si>
-    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
-  </si>
-  <si>
-    <t>6227605</t>
-  </si>
-  <si>
-    <t>DD8DF0569FF9985DE745D24A67351140</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>8145163</t>
-  </si>
-  <si>
-    <t>Hombre</t>
-  </si>
-  <si>
-    <t>subdirección financiera</t>
-  </si>
-  <si>
-    <t>05/07/2023</t>
-  </si>
-  <si>
-    <t>DERIVADO DEL CIERRE DEL SEGUNDO TRIMESTRE DEL AÑO 2023 (ABRIL, MAYO Y JUNIO), EL COLEGIO DE BACHILLERES DEL ESTADO DE TLAXCALA, NO  REALIZO ANTE LA DIRECCIÓN GENERAL DE RECURSOS MATERIALES, SERVICIOS Y ADQUISICIONES DEL ESTADO DE TLAXCALA, PROCEDIMIENTO DE ADQUISICIONES MEDIANTE LICITACIÓN PÚBLICA TODA VEZ QUE COMO LO MENCIONA EL ARTÍCULO 42 DE LA LEY DE ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS DEL SECTOR PÚBLICO: “ARTÍCULO 42. LAS DEPENDENCIAS Y ENTIDADES, BAJO SU RESPONSABILIDAD, PODRÁN CONTRATAR ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS, SIN SUJETARSE AL PROCEDIMIENTO DE LICITACIÓN PÚBLICA, A TRAVÉS DE LOS DE INVITACIÓN A CUANDO MENOS TRES PERSONAS O DE ADJUDICACIÓN DIRECTA, CUANDO EL IMPORTE DE CADA OPERACIÓN NO EXCEDA LOS MONTOS MÁXIMOS QUE AL EFECTO SE ESTABLECERÁN EN EL PRESUPUESTO DE EGRESOS DE LA FEDERACIÓN, SIEMPRE QUE LAS OPERACIONES NO SE FRACCIONEN PARA QUEDAR COMPRENDIDAS EN LOS SUPUESTOS DE EXCEPCIÓN A LA LICITACIÓN PÚBLICA A QUE SE REFIERE ESTE ARTÍCULO. SI EL MONTO DE LA OPERACIÓN CORRESPONDE A UNA INVITACIÓN A CUANDO MENOS TRES PERSONAS, LA PROCEDENCIA DE LA ADJUDICACIÓN DIRECTA SÓLO PODRÁ SER AUTORIZADA POR EL OFICIAL MAYOR O EQUIVALENTE.”…</t>
-  </si>
-  <si>
-    <t>5C969468A5A5ED89620286B5BC2CB530</t>
-  </si>
-  <si>
-    <t>8145164</t>
+    <t>Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>4584A3FC06C58119C0BE1C1F90FEC9B0</t>
+  </si>
+  <si>
+    <t>01/10/2021</t>
+  </si>
+  <si>
+    <t>31/12/2021</t>
+  </si>
+  <si>
+    <t>2104746</t>
+  </si>
+  <si>
+    <t>05/10/2021</t>
+  </si>
+  <si>
+    <t>DERIVADO DEL CIERRE DEL CUARTO TRIMESTRE DEL AÑO 2021 (OCTUBRE, NOVIEMBRE, DICIEMBRE), EL COLEGIO DE BACHILLERES DEL ESTADO DE TLAXCALA, NO  REALIZO ANTE LA DIRECCIÓN GENERAL DE RECURSOS MATERIALES, SERVICIOS Y ADQUISICIONES DEL ESTADO DE TLAXCALA, PROCEDIMIENTO DE ADQUISICIONES MEDIANTE INVITACIÓN A CUANDO MENOS TRES PERSONAS, TODA VEZ QUE COMO LO MENCIONA EL ARTÍCULO 42 DE LA LEY DE ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS DEL SECTOR PÚBLICO: “Artículo 42. las dependencias y entidades, bajo su responsabilidad, podrán contratar adquisiciones, arrendamientos y servicios, sin sujetarse al procedimiento de licitación pública, a través de los de invitación a cuando menos tres personas o de adjudicación directa, cuando el importe de cada operación no exceda los montos máximos que al efecto se establecerán en el presupuesto de egresos de la federación, siempre que las operaciones no se fraccionen para quedar comprendidas en los supuestos de excepción a la licitación pública a que se refiere este artículo. Si el monto de la operación corresponde a una invitación a cuando menos tres personas, la procedencia de la adjudicación directa sólo podrá ser autorizada por el oficial mayor o equivalente.”…</t>
+  </si>
+  <si>
+    <t>40B70B746CF10E79757CC6E308ECB8B6</t>
+  </si>
+  <si>
+    <t>2104747</t>
+  </si>
+  <si>
+    <t>DERIVADO DEL CIERRE DEL CUARTO TRIMESTRE DEL AÑO 2021 (OCTUBRE, NOVIEMBRE, DICIEMBRE), EL COLEGIO DE BACHILLERES DEL ESTADO DE TLAXCALA, NO  REALIZO ANTE LA DIRECCIÓN GENERAL DE RECURSOS MATERIALES, SERVICIOS Y ADQUISICIONES DEL ESTADO DE TLAXCALA, PROCEDIMIENTO DE ADQUISICIONES MEDIANTE OTRO TIPO, CONFORME AL ARTÍCULO 42 DE LA LEY DE ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS DEL SECTOR PÚBLICO POR LO QUE NO SE TIENE INFORMACIÓN QUE REPORTAR.</t>
+  </si>
+  <si>
+    <t>884A2753B4497E82053278F4D7D17679</t>
+  </si>
+  <si>
+    <t>2104745</t>
+  </si>
+  <si>
+    <t>DERIVADO DEL CIERRE DEL CUARTO TRIMESTRE DEL AÑO 2021 (OCTUBRE, NOVIEMBRE, DICIEMBRE), EL COLEGIO DE BACHILLERES DEL ESTADO DE TLAXCALA, NO  REALIZO ANTE LA DIRECCIÓN GENERAL DE RECURSOS MATERIALES, SERVICIOS Y ADQUISICIONES DEL ESTADO DE TLAXCALA, PROCEDIMIENTO DE ADQUISICIONES MEDIANTE LICITACIÓN PÚBLICA TODA VEZ QUE COMO LO MENCIONA EL ARTÍCULO 42 DE LA LEY DE ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS DEL SECTOR PÚBLICO: “Artículo 42. las dependencias y entidades, bajo su responsabilidad, podrán contratar adquisiciones, arrendamientos y servicios, sin sujetarse al procedimiento de licitación pública, a través de los de invitación a cuando menos tres personas o de adjudicación directa, cuando el importe de cada operación no exceda los montos máximos que al efecto se establecerán en el presupuesto de egresos de la federación, siempre que las operaciones no se fraccionen para quedar comprendidas en los supuestos de excepción a la licitación pública a que se refiere este artículo. Si el monto de la operación corresponde a una invitación a cuando menos tres personas, la procedencia de la adjudicación directa sólo podrá ser autorizada por el oficial mayor o equivalente.”…</t>
   </si>
   <si>
     <t>Licitación pública</t>
   </si>
   <si>
+    <t>1131763</t>
+  </si>
+  <si>
+    <t>VER NOTA</t>
+  </si>
+  <si>
     <t>Invitación a cuando menos tres personas</t>
   </si>
   <si>
+    <t>1131764</t>
+  </si>
+  <si>
     <t>Otro (especificar)</t>
   </si>
   <si>
+    <t>1131765</t>
+  </si>
+  <si>
     <t>Obra pública</t>
   </si>
   <si>
@@ -670,9 +669,6 @@
     <t>Internacional</t>
   </si>
   <si>
-    <t>Mujer</t>
-  </si>
-  <si>
     <t>Carretera</t>
   </si>
   <si>
@@ -997,9 +993,6 @@
     <t>56478</t>
   </si>
   <si>
-    <t>77803</t>
-  </si>
-  <si>
     <t>56479</t>
   </si>
   <si>
@@ -1018,25 +1011,28 @@
     <t>Razón Social</t>
   </si>
   <si>
-    <t>Sexo (catálogo)</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFC de los posibles contratantes </t>
   </si>
   <si>
-    <t>AE57B1F2A7057647699CCC19BF4A55CF</t>
-  </si>
-  <si>
-    <t>VER NOTA</t>
-  </si>
-  <si>
-    <t>AE57B1F2A7057647B7A30FE4846CD607</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E07F561E97CBDD8FF2F</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E0726EB72A9072CE7E1</t>
+    <t>4E88255EDEB2EE6FCF80554B75FA302D</t>
+  </si>
+  <si>
+    <t>34311CC5F0B874914323CED132508066</t>
+  </si>
+  <si>
+    <t>0C781AC3D41640F4CA4E994ED6894F93</t>
+  </si>
+  <si>
+    <t>C1F059227C94A6E37C6BF1E3BDA48631</t>
+  </si>
+  <si>
+    <t>4C30BA998E1746F8FA7FF81867746234</t>
+  </si>
+  <si>
+    <t>EB470DC1A872BB21B484B064ABB82716</t>
+  </si>
+  <si>
+    <t>D8468BFB773EBB9175E593BC3772AA2E</t>
   </si>
   <si>
     <t>56480</t>
@@ -1051,9 +1047,6 @@
     <t>56483</t>
   </si>
   <si>
-    <t>77807</t>
-  </si>
-  <si>
     <t>56484</t>
   </si>
   <si>
@@ -1063,16 +1056,25 @@
     <t>RFC de las personas físicas o morales que presentaron una proposición u oferta</t>
   </si>
   <si>
-    <t>AE57B1F2A7057647198C40CBFF5E7988</t>
-  </si>
-  <si>
-    <t>AE57B1F2A7057647210B96B69A7B68AE</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E0781340809ED168F78</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E07F96166D0A49F1136</t>
+    <t>CD6ABEDDC31FE41D67AE15B19E8B11A9</t>
+  </si>
+  <si>
+    <t>08C5B745989413703A5A182382505665</t>
+  </si>
+  <si>
+    <t>2F9B30FC28E615CB433E955B42D04D39</t>
+  </si>
+  <si>
+    <t>68EE6CC2DF861BF643DE95F1583EA2DB</t>
+  </si>
+  <si>
+    <t>4BBA28BA40CD093D8A54CE4BD009634B</t>
+  </si>
+  <si>
+    <t>32B9BF08DC40A06AF2BBE1DB8EAC5097</t>
+  </si>
+  <si>
+    <t>27C2ABB73FCDB60596423681F189DCF1</t>
   </si>
   <si>
     <t>56485</t>
@@ -1087,25 +1089,31 @@
     <t>56488</t>
   </si>
   <si>
-    <t>77802</t>
-  </si>
-  <si>
     <t>56489</t>
   </si>
   <si>
     <t>RFC de las personas físicas o morales asistentes a la junta de aclaraciones</t>
   </si>
   <si>
-    <t>AE57B1F2A7057647C1EEA04A7B84C11B</t>
-  </si>
-  <si>
-    <t>AE57B1F2A7057647A47A3726C1A9769B</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E0756B1A2F240729683</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E07F9116FAE5A5C684E</t>
+    <t>AF6CC3C3089D2F066644FF608F25AF01</t>
+  </si>
+  <si>
+    <t>EAD79731930BA52FCFA44883808041D1</t>
+  </si>
+  <si>
+    <t>CF5808FFF04B3AFD646555963FF2BB19</t>
+  </si>
+  <si>
+    <t>1D94F4BA1D41CFA7F978C6D37EC4BD01</t>
+  </si>
+  <si>
+    <t>F4FD444340E3F4AD723005F33C9C72BF</t>
+  </si>
+  <si>
+    <t>BC001BA246DC67D62AFC68271461049E</t>
+  </si>
+  <si>
+    <t>F960BDFFDDF1105F016A35266D7A786A</t>
   </si>
   <si>
     <t>56490</t>
@@ -1117,9 +1125,6 @@
     <t>56492</t>
   </si>
   <si>
-    <t>77812</t>
-  </si>
-  <si>
     <t>56494</t>
   </si>
   <si>
@@ -1141,16 +1146,25 @@
     <t>Cargo que ocupa el Servidor Público dentro del SO</t>
   </si>
   <si>
-    <t>AE57B1F2A705764779B61816D980A4B3</t>
-  </si>
-  <si>
-    <t>8F6BD8FAA81ECEE165ACFF7501CB64B2</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E071AA4EF8DFBF8ECC6</t>
-  </si>
-  <si>
-    <t>0724DB38E7E5673A4A4BEFCB0C08057F</t>
+    <t>782253345B5902D28E2B77FAE08BF6DE</t>
+  </si>
+  <si>
+    <t>F8070E4B27F4CFEB6919F0AD56262979</t>
+  </si>
+  <si>
+    <t>E03D7A3F531770CC7992B2A4F2D93C26</t>
+  </si>
+  <si>
+    <t>CF650C93C246DF7765A4B76D7D52236E</t>
+  </si>
+  <si>
+    <t>8A5B151F25CDCC6AF9CD5C07964037D1</t>
+  </si>
+  <si>
+    <t>11CD65B580E9571B8528A3F555A3A769</t>
+  </si>
+  <si>
+    <t>311DB08D1515FE6D9BE81207835C9F30</t>
   </si>
   <si>
     <t>56495</t>
@@ -1159,16 +1173,25 @@
     <t>Partida Presupuestal</t>
   </si>
   <si>
-    <t>AE57B1F2A7057647238907243E9A32CD</t>
-  </si>
-  <si>
-    <t>8F6BD8FAA81ECEE1860FD747DFA68EB9</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E07727D24755043F76B</t>
-  </si>
-  <si>
-    <t>0724DB38E7E5673A976AACB9BD92FFF7</t>
+    <t>BE906E8C0D403440C05977056056DF00</t>
+  </si>
+  <si>
+    <t>0B06A4E5F5E0D0BD610D4096E8F41261</t>
+  </si>
+  <si>
+    <t>08868E06A42B76571748FAB5DF42E7CC</t>
+  </si>
+  <si>
+    <t>BE7D4977430ECDD11EF792E6980014C3</t>
+  </si>
+  <si>
+    <t>628E28DE3F8A61401C7DB0B45D67DE68</t>
+  </si>
+  <si>
+    <t>9C4558582617B11CEE4A123A2050429B</t>
+  </si>
+  <si>
+    <t>76CF42C5292FFCFE02A0CFE86AF74CDD</t>
   </si>
   <si>
     <t>56496</t>
@@ -1195,16 +1218,25 @@
     <t>Hipervínculo al documento del convenio</t>
   </si>
   <si>
-    <t>AE57B1F2A7057647CBE5A1FF3D0F6DD6</t>
-  </si>
-  <si>
-    <t>8F6BD8FAA81ECEE1705D09DFBF7694FE</t>
-  </si>
-  <si>
-    <t>7DE8CFD837056E07935E65299B6D6C98</t>
-  </si>
-  <si>
-    <t>0724DB38E7E5673A1A1585CB788C3E87</t>
+    <t>1EB120C7EEF576AE8BCDD29FAB9DB158</t>
+  </si>
+  <si>
+    <t>0CB960859A60CCEB53EA96ECFE796AE3</t>
+  </si>
+  <si>
+    <t>E926B6092F448B0FA874BBA0F467ABA7</t>
+  </si>
+  <si>
+    <t>599803F165591B9B80A24A2A4EAABF32</t>
+  </si>
+  <si>
+    <t>CD7FD7BA7EA1F8D1E6A0A7963DAA18C8</t>
+  </si>
+  <si>
+    <t>0A279852D0DC778718AE6BB36175189E</t>
+  </si>
+  <si>
+    <t>6553AB0D106F3529CDD4F43691BAC665</t>
   </si>
 </sst>
 </file>
@@ -1600,14 +1632,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CD9"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -1626,73 +1658,72 @@
     <col min="21" max="21" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="69.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="63.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="74.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="69" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="66.5703125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="64.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="77.28515625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="73" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="84" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="60" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="62.5703125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="60.85546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="48.28515625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="50.42578125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="44" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="44.42578125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="68.28515625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="82" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="51.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="57" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="51.5703125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="76.5703125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="82" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="20" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="255" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="61" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="74.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="69" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="77.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="73" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="84" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="60" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="62.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="44" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="82" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="57" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="82" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="20" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1709,7 +1740,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1724,7 +1755,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:82" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:81" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1792,13 +1823,13 @@
         <v>11</v>
       </c>
       <c r="X4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="s">
         <v>8</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>6</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>8</v>
       </c>
       <c r="AA4" t="s">
         <v>6</v>
@@ -1807,34 +1838,34 @@
         <v>6</v>
       </c>
       <c r="AC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="s">
         <v>6</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AK4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL4" t="s">
         <v>11</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>6</v>
       </c>
       <c r="AM4" t="s">
         <v>11</v>
@@ -1858,10 +1889,10 @@
         <v>11</v>
       </c>
       <c r="AT4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="s">
         <v>7</v>
@@ -1870,7 +1901,7 @@
         <v>7</v>
       </c>
       <c r="AX4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="s">
         <v>12</v>
@@ -1882,7 +1913,7 @@
         <v>12</v>
       </c>
       <c r="BB4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="s">
         <v>6</v>
@@ -1891,58 +1922,58 @@
         <v>6</v>
       </c>
       <c r="BE4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BG4" t="s">
         <v>7</v>
       </c>
       <c r="BH4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="s">
         <v>10</v>
       </c>
       <c r="BJ4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BL4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BM4" t="s">
         <v>6</v>
       </c>
       <c r="BN4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BO4" t="s">
         <v>11</v>
       </c>
       <c r="BP4" t="s">
+        <v>10</v>
+      </c>
+      <c r="BQ4" t="s">
         <v>11</v>
       </c>
-      <c r="BQ4" t="s">
-        <v>10</v>
-      </c>
       <c r="BR4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BS4" t="s">
         <v>8</v>
       </c>
       <c r="BT4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BV4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="s">
         <v>10</v>
@@ -1954,22 +1985,19 @@
         <v>10</v>
       </c>
       <c r="BZ4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CA4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="CC4" t="s">
-        <v>13</v>
-      </c>
-      <c r="CD4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:82" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:81" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -2210,13 +2238,10 @@
       <c r="CC5" t="s">
         <v>94</v>
       </c>
-      <c r="CD5" t="s">
+    </row>
+    <row r="6" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2298,752 +2323,987 @@
       <c r="CA6" s="5"/>
       <c r="CB6" s="5"/>
       <c r="CC6" s="5"/>
-      <c r="CD6" s="5"/>
-    </row>
-    <row r="7" spans="1:82" ht="39" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:81" ht="39" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AG7" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AG7" s="2" t="s">
+      <c r="AH7" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AH7" s="2" t="s">
+      <c r="AI7" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AM7" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AN7" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AN7" s="2" t="s">
+      <c r="AO7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AP7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AP7" s="2" t="s">
+      <c r="AQ7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AQ7" s="2" t="s">
+      <c r="AR7" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AS7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AS7" s="2" t="s">
+      <c r="AT7" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="AT7" s="2" t="s">
+      <c r="AU7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AU7" s="2" t="s">
+      <c r="AV7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AV7" s="2" t="s">
+      <c r="AW7" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="AW7" s="2" t="s">
+      <c r="AX7" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="AX7" s="2" t="s">
+      <c r="AY7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="AY7" s="2" t="s">
+      <c r="AZ7" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AZ7" s="2" t="s">
+      <c r="BA7" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="BA7" s="2" t="s">
+      <c r="BB7" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="BB7" s="2" t="s">
+      <c r="BC7" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="BC7" s="2" t="s">
+      <c r="BD7" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="BD7" s="2" t="s">
+      <c r="BE7" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="BE7" s="2" t="s">
+      <c r="BF7" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="BF7" s="2" t="s">
+      <c r="BG7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="BG7" s="2" t="s">
+      <c r="BH7" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="BH7" s="2" t="s">
+      <c r="BI7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="BI7" s="2" t="s">
+      <c r="BJ7" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="BJ7" s="2" t="s">
+      <c r="BK7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="BK7" s="2" t="s">
+      <c r="BL7" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="BL7" s="2" t="s">
+      <c r="BM7" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="BM7" s="2" t="s">
+      <c r="BN7" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="BN7" s="2" t="s">
+      <c r="BO7" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="BO7" s="2" t="s">
+      <c r="BP7" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="BP7" s="2" t="s">
+      <c r="BQ7" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="BQ7" s="2" t="s">
+      <c r="BR7" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="BR7" s="2" t="s">
+      <c r="BS7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="BS7" s="2" t="s">
+      <c r="BT7" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="BT7" s="2" t="s">
+      <c r="BU7" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="BU7" s="2" t="s">
+      <c r="BV7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="BV7" s="2" t="s">
+      <c r="BW7" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="BW7" s="2" t="s">
+      <c r="BX7" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="BX7" s="2" t="s">
+      <c r="BY7" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="BY7" s="2" t="s">
+      <c r="BZ7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="BZ7" s="2" t="s">
+      <c r="CA7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="CA7" s="2" t="s">
+      <c r="CB7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="CB7" s="2" t="s">
+      <c r="CC7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="CC7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:81" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="CD7" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:82" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="I8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AP8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AV8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AX8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AY8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BA8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BC8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BD8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BE8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BF8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BG8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BH8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BJ8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="BK8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BL8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BM8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BN8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BO8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BP8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BQ8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BR8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BS8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BT8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="BU8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BW8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BX8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BY8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BZ8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="CA8" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="CB8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="CC8" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:81" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="X8" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AL8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AM8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AN8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AP8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AQ8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AR8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AS8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AT8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AU8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AW8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AX8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AY8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AZ8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BA8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BB8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BC8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BD8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BE8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BF8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BG8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BH8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BI8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BJ8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BK8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="BL8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BM8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BN8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BO8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BP8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BQ8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BR8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BS8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BT8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BU8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="BV8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BW8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BX8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BY8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BZ8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="CA8" s="3" t="s">
+      <c r="I9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AV9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AX9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AY9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BA9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BC9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BD9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BE9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BF9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BG9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BH9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BJ9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="BK9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BL9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BM9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BN9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BO9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BP9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BQ9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BR9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BS9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BT9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="BU9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BW9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BX9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BY9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BZ9" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="CA9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="CB9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="CC9" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="CB8" s="3" t="s">
+    </row>
+    <row r="10" spans="1:81" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="CC8" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="CD8" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="9" spans="1:82" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="I10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AV10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AX10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AY10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BA10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BC10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BD10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BE10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BF10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BG10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BH10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BJ10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BL10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BM10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BN10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BO10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BP10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BQ10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BR10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BS10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BT10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="BU10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BW10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BX10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BY10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BZ10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="CA10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="CB10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="CC10" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AM9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AN9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AP9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AQ9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AR9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AS9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AT9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AU9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AW9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AX9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AY9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AZ9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BA9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BB9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BC9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BD9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BE9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BF9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BG9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BH9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BI9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BJ9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BK9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="BL9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BM9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BN9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BO9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BP9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BQ9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BR9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BS9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BT9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BU9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="BV9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BW9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BX9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BY9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="BZ9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="CA9" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="CB9" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="CC9" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="CD9" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:CD6"/>
+    <mergeCell ref="A6:CC6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -3051,36 +3311,33 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E195">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F199">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F195">
       <formula1>Hidden_25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G199">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G195">
       <formula1>Hidden_36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X199">
-      <formula1>Hidden_423</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y195">
+      <formula1>Hidden_424</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z199">
-      <formula1>Hidden_525</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC8:AC195">
+      <formula1>Hidden_528</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AD8:AD199">
-      <formula1>Hidden_629</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AJ8:AJ195">
+      <formula1>Hidden_635</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AK8:AK199">
-      <formula1>Hidden_736</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BK8:BK195">
+      <formula1>Hidden_762</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BL8:BL199">
-      <formula1>Hidden_863</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BR8:BR195">
+      <formula1>Hidden_869</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BS8:BS199">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BS8:BS195">
       <formula1>Hidden_970</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BT8:BT199">
-      <formula1>Hidden_1071</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3089,22 +3346,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3114,17 +3366,232 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>308</v>
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3134,20 +3601,19 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="84" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -3161,183 +3627,441 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="F2" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="G2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
-      <formula1>Hidden_1_Tabla_4364446</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="78.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>204</v>
+      <c r="B6" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3347,20 +4071,19 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="84" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="71.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="53.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -3374,183 +4097,317 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="D2" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="E2" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="F2" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="G2" t="s">
-        <v>331</v>
-      </c>
-      <c r="H2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
-      <formula1>Hidden_1_Tabla_4364736</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>204</v>
+      <c r="B6" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3560,423 +4417,201 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="78.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>339</v>
+        <v>382</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>383</v>
       </c>
       <c r="E2" t="s">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="F2" t="s">
-        <v>342</v>
-      </c>
-      <c r="G2" t="s">
-        <v>343</v>
-      </c>
-      <c r="H2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>316</v>
+        <v>386</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>317</v>
+        <v>387</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>318</v>
+        <v>388</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>347</v>
+        <v>391</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
-      <formula1>Hidden_1_Tabla_4364746</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="71.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
-      <formula1>Hidden_1_Tabla_4364755</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>204</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3991,239 +4626,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4238,27 +4651,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -4273,12 +4686,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -4288,17 +4701,137 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4308,137 +4841,212 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>230</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -4448,212 +5056,167 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>231</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>258</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4663,167 +5226,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -4838,17 +5256,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
